--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -3245,7 +3245,9 @@
       <c r="G49" s="10" t="n">
         <v>181.5</v>
       </c>
-      <c r="H49" s="10" t="n"/>
+      <c r="H49" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="I49" s="15">
         <f>(H49-G49)/G49</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="42" customHeight="1"/>
   <cols>
     <col width="5.140625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -3268,6 +3268,165 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>46288.41666666666</v>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="15">
+        <f>(H50-G50)/G50</f>
+        <v/>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t>2026年12月22日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>中挥发份性焦煤</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>46288.41666666666</v>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>10 批量/64000吨/</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="15">
+        <f>(H51-G51)/G51</f>
+        <v/>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>3/23/2027 /根据供应计划,在送货时间内完成供应/</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
+          <t>供应商送到买方指定的中国甘其毛都口岸的海关监管区</t>
+        </is>
+      </c>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
+          <t>公路， 铁路</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>中挥发份性焦煤</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>46288.58333333334</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>10 批量/64000吨/</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="15">
+        <f>(H52-G52)/G52</f>
+        <v/>
+      </c>
+      <c r="J52" s="13" t="inlineStr">
+        <is>
+          <t>3/23/2027 /根据供应计划,在送货时间内完成供应/</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>供应商送到买方指定的中国满都拉口岸的海关监管区</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>公路， 铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3300,7 +3300,9 @@
       <c r="G50" s="10" t="n">
         <v>1150</v>
       </c>
-      <c r="H50" s="10" t="n"/>
+      <c r="H50" s="10" t="n">
+        <v>1290</v>
+      </c>
       <c r="I50" s="15">
         <f>(H50-G50)/G50</f>
         <v/>
@@ -3353,7 +3355,9 @@
       <c r="G51" s="10" t="n">
         <v>181.5</v>
       </c>
-      <c r="H51" s="10" t="n"/>
+      <c r="H51" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="I51" s="15">
         <f>(H51-G51)/G51</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3410,7 +3410,9 @@
       <c r="G52" s="10" t="n">
         <v>181.5</v>
       </c>
-      <c r="H52" s="10" t="n"/>
+      <c r="H52" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="I52" s="15">
         <f>(H52-G52)/G52</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="42" customHeight="1"/>
   <cols>
     <col width="5.140625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -3433,6 +3433,59 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>鉬</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>钼含量不低于44%的钼精矿</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>额尔登特矿业公司国资企业</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>46289.625</v>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>14 批量/499.408吨/</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>28504.17</v>
+      </c>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="15">
+        <f>(H53-G53)/G53</f>
+        <v/>
+      </c>
+      <c r="J53" s="13" t="inlineStr">
+        <is>
+          <t>將於2026年11月30日前交付。 DAP (国际贸易术语解释通则2020及其任何修订) 蒙古/中国边境 (二连)。</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>中国二连浩特铁路车站精矿装卸作业区</t>
+        </is>
+      </c>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
+          <t>铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -66,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -77,13 +76,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -546,7 +551,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="7" t="n">
         <v>46261.41666666666</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -565,7 +570,7 @@
       <c r="H2" s="2" t="n">
         <v>1340</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="8">
         <f>(H2-G2)/G2</f>
         <v/>
       </c>
@@ -602,7 +607,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="7" t="n">
         <v>46261.41666666666</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -621,7 +626,7 @@
       <c r="H3" s="6" t="n">
         <v>190.5</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="8">
         <f>(H3-G3)/G3</f>
         <v/>
       </c>
@@ -657,7 +662,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="7" t="n">
         <v>46262.41666666666</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -676,7 +681,7 @@
       <c r="H4" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="8">
         <f>(H4-G4)/G4</f>
         <v/>
       </c>
@@ -713,7 +718,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="7" t="n">
         <v>46262.41666666666</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -732,7 +737,7 @@
       <c r="H5" s="6" t="n">
         <v>198.5</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="8">
         <f>(H5-G5)/G5</f>
         <v/>
       </c>
@@ -768,7 +773,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="7" t="n">
         <v>46262.5</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -787,7 +792,7 @@
       <c r="H6" s="6" t="n">
         <v>194.5</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="8">
         <f>(H6-G6)/G6</f>
         <v/>
       </c>
@@ -823,7 +828,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="7" t="n">
         <v>46265.41666666666</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -842,7 +847,7 @@
       <c r="H7" s="2" t="n">
         <v>1515</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="8">
         <f>(H7-G7)/G7</f>
         <v/>
       </c>
@@ -879,7 +884,7 @@
           <t>坎加德勘探 有限责任公司</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="7" t="n">
         <v>46266.41666666666</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -898,7 +903,7 @@
       <c r="H8" s="2" t="n">
         <v>1205</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="8">
         <f>(H8-G8)/G8</f>
         <v/>
       </c>
@@ -935,7 +940,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="7" t="n">
         <v>46267.41666666666</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -954,7 +959,7 @@
       <c r="H9" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="8">
         <f>(H9-G9)/G9</f>
         <v/>
       </c>
@@ -991,7 +996,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="7" t="n">
         <v>46267.45833333334</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1010,7 +1015,7 @@
       <c r="H10" s="6" t="n">
         <v>211.5</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="8">
         <f>(H10-G10)/G10</f>
         <v/>
       </c>
@@ -1046,7 +1051,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="7" t="n">
         <v>46267.58333333334</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1065,7 +1070,7 @@
       <c r="H11" s="6" t="n">
         <v>212.5</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="8">
         <f>(H11-G11)/G11</f>
         <v/>
       </c>
@@ -1101,7 +1106,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="7" t="n">
         <v>46268.41666666666</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1120,7 +1125,7 @@
       <c r="H12" s="6" t="n">
         <v>171.4</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="8">
         <f>(H12-G12)/G12</f>
         <v/>
       </c>
@@ -1157,7 +1162,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="7" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1176,7 +1181,7 @@
       <c r="H13" s="6" t="n">
         <v>210.5</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="8">
         <f>(H13-G13)/G13</f>
         <v/>
       </c>
@@ -1212,7 +1217,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="7" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1231,7 +1236,7 @@
       <c r="H14" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="8">
         <f>(H14-G14)/G14</f>
         <v/>
       </c>
@@ -1268,7 +1273,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="7" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1287,7 +1292,7 @@
       <c r="H15" s="2" t="n">
         <v>1445</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="8">
         <f>(H15-G15)/G15</f>
         <v/>
       </c>
@@ -1324,7 +1329,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="7" t="n">
         <v>46269.58333333334</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1343,7 +1348,7 @@
       <c r="H16" s="6" t="n">
         <v>208.5</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="8">
         <f>(H16-G16)/G16</f>
         <v/>
       </c>
@@ -1379,7 +1384,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="7" t="n">
         <v>46272.41666666666</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1398,7 +1403,7 @@
       <c r="H17" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="8">
         <f>(H17-G17)/G17</f>
         <v/>
       </c>
@@ -1435,7 +1440,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="7" t="n">
         <v>46272.41666666666</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1454,7 +1459,7 @@
       <c r="H18" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="8">
         <f>(H18-G18)/G18</f>
         <v/>
       </c>
@@ -1491,7 +1496,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="7" t="n">
         <v>46272.5</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1510,7 +1515,7 @@
       <c r="H19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="8">
         <f>(H19-G19)/G19</f>
         <v/>
       </c>
@@ -1547,7 +1552,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="7" t="n">
         <v>46273.41666666666</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1566,7 +1571,7 @@
       <c r="H20" s="6" t="n">
         <v>193.5</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="8">
         <f>(H20-G20)/G20</f>
         <v/>
       </c>
@@ -1603,7 +1608,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="7" t="n">
         <v>46274.41666666666</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1622,7 +1627,7 @@
       <c r="H21" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="8">
         <f>(H21-G21)/G21</f>
         <v/>
       </c>
@@ -1659,7 +1664,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="7" t="n">
         <v>46274.41666666666</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1678,7 +1683,7 @@
       <c r="H22" s="2" t="n">
         <v>1435</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="8">
         <f>(H22-G22)/G22</f>
         <v/>
       </c>
@@ -1715,7 +1720,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="7" t="n">
         <v>46274.66666666666</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1734,7 +1739,7 @@
       <c r="H23" s="6" t="n">
         <v>187.5</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="8">
         <f>(H23-G23)/G23</f>
         <v/>
       </c>
@@ -1771,7 +1776,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="7" t="n">
         <v>46275.45833333334</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1790,7 +1795,7 @@
       <c r="H24" s="6" t="n">
         <v>120.5</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="8">
         <f>(H24-G24)/G24</f>
         <v/>
       </c>
@@ -1826,7 +1831,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="7" t="n">
         <v>46276.41666666666</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1845,7 +1850,7 @@
       <c r="H25" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="8">
         <f>(H25-G25)/G25</f>
         <v/>
       </c>
@@ -1881,7 +1886,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="7" t="n">
         <v>46276.41666666666</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1900,7 +1905,7 @@
       <c r="H26" s="2" t="n">
         <v>1445</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="8">
         <f>(H26-G26)/G26</f>
         <v/>
       </c>
@@ -1936,7 +1941,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="7" t="n">
         <v>46276.45833333334</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1955,7 +1960,7 @@
       <c r="H27" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="8">
         <f>(H27-G27)/G27</f>
         <v/>
       </c>
@@ -1991,7 +1996,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="7" t="n">
         <v>46276.58333333334</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2010,7 +2015,7 @@
       <c r="H28" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="8">
         <f>(H28-G28)/G28</f>
         <v/>
       </c>
@@ -2046,7 +2051,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="7" t="n">
         <v>46276.625</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2065,7 +2070,7 @@
       <c r="H29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="8">
         <f>(H29-G29)/G29</f>
         <v/>
       </c>
@@ -2101,7 +2106,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="7" t="n">
         <v>46279.41666666666</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2120,7 +2125,7 @@
       <c r="H30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="8">
         <f>(H30-G30)/G30</f>
         <v/>
       </c>
@@ -2156,7 +2161,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="7" t="n">
         <v>46279.41666666666</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2175,7 +2180,7 @@
       <c r="H31" s="2" t="n">
         <v>1420</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="8">
         <f>(H31-G31)/G31</f>
         <v/>
       </c>
@@ -2211,7 +2216,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="7" t="n">
         <v>46279.45833333334</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2230,7 +2235,7 @@
       <c r="H32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="8">
         <f>(H32-G32)/G32</f>
         <v/>
       </c>
@@ -2266,7 +2271,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="7" t="n">
         <v>46279.58333333334</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2285,7 +2290,7 @@
       <c r="H33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="8">
         <f>(H33-G33)/G33</f>
         <v/>
       </c>
@@ -2321,7 +2326,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="7" t="n">
         <v>46279.625</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2340,7 +2345,7 @@
       <c r="H34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="8">
         <f>(H34-G34)/G34</f>
         <v/>
       </c>
@@ -2376,7 +2381,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="7" t="n">
         <v>46280.41666666666</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2395,7 +2400,7 @@
       <c r="H35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="8">
         <f>(H35-G35)/G35</f>
         <v/>
       </c>
@@ -2431,7 +2436,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="7" t="n">
         <v>46280.58333333334</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2450,7 +2455,7 @@
       <c r="H36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="8">
         <f>(H36-G36)/G36</f>
         <v/>
       </c>
@@ -2486,7 +2491,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="7" t="n">
         <v>46281.41666666666</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2505,7 +2510,7 @@
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="8">
         <f>(H37-G37)/G37</f>
         <v/>
       </c>
@@ -2541,7 +2546,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="7" t="n">
         <v>46281.41666666666</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2560,7 +2565,7 @@
       <c r="H38" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="8">
         <f>(H38-G38)/G38</f>
         <v/>
       </c>
@@ -2596,7 +2601,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="7" t="n">
         <v>46281.58333333334</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2615,7 +2620,7 @@
       <c r="H39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="8">
         <f>(H39-G39)/G39</f>
         <v/>
       </c>
@@ -2651,7 +2656,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="7" t="n">
         <v>46282.41666666666</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2670,7 +2675,7 @@
       <c r="H40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="8">
         <f>(H40-G40)/G40</f>
         <v/>
       </c>
@@ -2706,7 +2711,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="7" t="n">
         <v>46282.58333333334</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2725,7 +2730,7 @@
       <c r="H41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="8">
         <f>(H41-G41)/G41</f>
         <v/>
       </c>
@@ -2761,7 +2766,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="7" t="n">
         <v>46283.41666666666</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2780,7 +2785,7 @@
       <c r="H42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="8">
         <f>(H42-G42)/G42</f>
         <v/>
       </c>
@@ -2816,7 +2821,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="7" t="n">
         <v>46283.41666666666</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2835,7 +2840,7 @@
       <c r="H43" s="2" t="n">
         <v>1255</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="8">
         <f>(H43-G43)/G43</f>
         <v/>
       </c>
@@ -2871,7 +2876,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="7" t="n">
         <v>46283.58333333334</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2890,7 +2895,7 @@
       <c r="H44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="8">
         <f>(H44-G44)/G44</f>
         <v/>
       </c>
@@ -2926,7 +2931,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="7" t="n">
         <v>46286.41666666666</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2945,7 +2950,7 @@
       <c r="H45" s="2" t="n">
         <v>1295</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="8">
         <f>(H45-G45)/G45</f>
         <v/>
       </c>
@@ -2981,7 +2986,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="7" t="n">
         <v>46286.41666666666</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -3000,7 +3005,7 @@
       <c r="H46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="8">
         <f>(H46-G46)/G46</f>
         <v/>
       </c>
@@ -3036,7 +3041,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="7" t="n">
         <v>46286.58333333334</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -3055,7 +3060,7 @@
       <c r="H47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="8">
         <f>(H47-G47)/G47</f>
         <v/>
       </c>
@@ -3091,7 +3096,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="7" t="n">
         <v>46287.41666666666</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -3110,7 +3115,7 @@
       <c r="H48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="8">
         <f>(H48-G48)/G48</f>
         <v/>
       </c>
@@ -3146,7 +3151,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="7" t="n">
         <v>46287.58333333334</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -3165,7 +3170,7 @@
       <c r="H49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I49" s="8">
         <f>(H49-G49)/G49</f>
         <v/>
       </c>
@@ -3201,7 +3206,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="7" t="n">
         <v>46288.41666666666</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -3220,7 +3225,7 @@
       <c r="H50" s="2" t="n">
         <v>1290</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I50" s="8">
         <f>(H50-G50)/G50</f>
         <v/>
       </c>
@@ -3256,7 +3261,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="7" t="n">
         <v>46288.41666666666</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -3275,7 +3280,7 @@
       <c r="H51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I51" s="8">
         <f>(H51-G51)/G51</f>
         <v/>
       </c>
@@ -3311,7 +3316,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="7" t="n">
         <v>46288.58333333334</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -3330,7 +3335,7 @@
       <c r="H52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I52" s="8">
         <f>(H52-G52)/G52</f>
         <v/>
       </c>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -456,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3355,6 +3356,112 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>46290.41666666666</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="8">
+        <f>(H53-G53)/G53</f>
+        <v/>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>2026年12月24日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>铜</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>铜含量为22.35%的铜精矿</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>额尔登特矿业公司国资企业</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>46290.625</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>7 批量/6342吨/</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>3318.59</v>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="8">
+        <f>(H54-G54)/G54</f>
+        <v/>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>將於2026年10月31日前交付。 DAP (国际贸易术语解释通则2020及其任何修订) 蒙古/中国边境 (二连)。</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>中国二连站铜矿粉装卸区</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3388,7 +3388,9 @@
       <c r="G53" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H53" s="2" t="n"/>
+      <c r="H53" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I53" s="8">
         <f>(H53-G53)/G53</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3389,7 +3389,7 @@
         <v>1150</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1150</v>
+        <v>1285</v>
       </c>
       <c r="I53" s="8">
         <f>(H53-G53)/G53</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3443,7 +3443,9 @@
       <c r="G54" s="2" t="n">
         <v>3318.59</v>
       </c>
-      <c r="H54" s="2" t="n"/>
+      <c r="H54" s="2" t="n">
+        <v>3318.59</v>
+      </c>
       <c r="I54" s="8">
         <f>(H54-G54)/G54</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3444,7 +3444,7 @@
         <v>3318.59</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>3318.59</v>
+        <v>3613.59</v>
       </c>
       <c r="I54" s="8">
         <f>(H54-G54)/G54</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -456,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3465,6 +3466,59 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>46293.41666666666</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="8">
+        <f>(H55-G55)/G55</f>
+        <v/>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>2026年12月27日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3498,7 +3498,9 @@
       <c r="G55" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H55" s="2" t="n"/>
+      <c r="H55" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I55" s="8">
         <f>(H55-G55)/G55</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3499,7 +3499,7 @@
         <v>1150</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>1150</v>
+        <v>1260</v>
       </c>
       <c r="I55" s="8">
         <f>(H55-G55)/G55</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -456,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3520,6 +3521,59 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>46295.41666666666</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="8">
+        <f>(H56-G56)/G56</f>
+        <v/>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>2026年12月29日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3553,7 +3553,9 @@
       <c r="G56" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H56" s="2" t="n"/>
+      <c r="H56" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I56" s="8">
         <f>(H56-G56)/G56</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3554,7 +3554,7 @@
         <v>1150</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1150</v>
+        <v>1265</v>
       </c>
       <c r="I56" s="8">
         <f>(H56-G56)/G56</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3576,6 +3576,59 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>中灰半硬焦煤</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>坎加德勘探 有限责任公司</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>46296.58333333334</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>3 批量/19200吨/</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="8">
+        <f>(H57-G57)/G57</f>
+        <v/>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026年12月30日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3608,7 +3608,9 @@
       <c r="G57" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="H57" s="2" t="n"/>
+      <c r="H57" s="2" t="n">
+        <v>500</v>
+      </c>
       <c r="I57" s="8">
         <f>(H57-G57)/G57</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3609,7 +3609,7 @@
         <v>500</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="I57" s="8">
         <f>(H57-G57)/G57</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3631,6 +3631,112 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1/3焦煤</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>塔万陶勒盖股份公司</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>46297.41666666666</v>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>157 批量/1004800吨/</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="8">
+        <f>(H58-G58)/G58</f>
+        <v/>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>2027-08-11 (DAP Mandula)</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>供应商送到买方指定的中国满都拉口岸的海关监管区</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>46297.41666666666</v>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="8">
+        <f>(H59-G59)/G59</f>
+        <v/>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>2026年12月31日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3663,7 +3663,9 @@
       <c r="G58" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="H58" s="2" t="n"/>
+      <c r="H58" s="2" t="n">
+        <v>101</v>
+      </c>
       <c r="I58" s="8">
         <f>(H58-G58)/G58</f>
         <v/>
@@ -3716,7 +3718,9 @@
       <c r="G59" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H59" s="2" t="n"/>
+      <c r="H59" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I59" s="8">
         <f>(H59-G59)/G59</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3664,7 +3664,7 @@
         <v>101</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="I58" s="8">
         <f>(H58-G58)/G58</f>
@@ -3719,7 +3719,7 @@
         <v>1150</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1150</v>
+        <v>1265</v>
       </c>
       <c r="I59" s="8">
         <f>(H59-G59)/G59</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -456,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3740,6 +3741,59 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="8">
+        <f>(H60-G60)/G60</f>
+        <v/>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月02日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3773,7 +3773,9 @@
       <c r="G60" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H60" s="2" t="n"/>
+      <c r="H60" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I60" s="8">
         <f>(H60-G60)/G60</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3774,7 +3774,7 @@
         <v>1150</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1150</v>
+        <v>1255</v>
       </c>
       <c r="I60" s="8">
         <f>(H60-G60)/G60</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3773,9 +3773,7 @@
       <c r="G60" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H60" s="2" t="n">
-        <v>1255</v>
-      </c>
+      <c r="H60" s="2" t="n"/>
       <c r="I60" s="8">
         <f>(H60-G60)/G60</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3794,6 +3794,112 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>洗选半软焦煤</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>塔万陶勒盖股份公司</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>157 批量/1004800吨/</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="8">
+        <f>(H61-G61)/G61</f>
+        <v/>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>2027-10-05 (DAP Ganqimaodu)</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>供应商送到买方指定的中国甘其毛都口岸的海关监管区</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>铁</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Fe-65%</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Mongolrostsvetmet SOE /Erdenes Critical Minerals SOE/</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>1 批量/3300吨/</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="8">
+        <f>(H62-G62)/G62</f>
+        <v/>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2027年10月</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>二连浩特铁路站</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3826,7 +3826,9 @@
       <c r="G61" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="H61" s="2" t="n"/>
+      <c r="H61" s="2" t="n">
+        <v>128</v>
+      </c>
       <c r="I61" s="8">
         <f>(H61-G61)/G61</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3827,7 +3827,7 @@
         <v>128</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>128</v>
+        <v>152.5</v>
       </c>
       <c r="I61" s="8">
         <f>(H61-G61)/G61</f>
@@ -3881,7 +3881,9 @@
       <c r="G62" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="H62" s="2" t="n"/>
+      <c r="H62" s="2" t="n">
+        <v>85</v>
+      </c>
       <c r="I62" s="8">
         <f>(H62-G62)/G62</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3827,7 +3827,7 @@
         <v>128</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>152.5</v>
+        <v>153</v>
       </c>
       <c r="I61" s="8">
         <f>(H61-G61)/G61</f>
@@ -3882,7 +3882,7 @@
         <v>85</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I62" s="8">
         <f>(H62-G62)/G62</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3904,6 +3904,59 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>46302.41666666666</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="8">
+        <f>(H63-G63)/G63</f>
+        <v/>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月04日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3936,7 +3936,9 @@
       <c r="G63" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H63" s="2" t="n"/>
+      <c r="H63" s="2" t="n">
+        <v>1155</v>
+      </c>
       <c r="I63" s="8">
         <f>(H63-G63)/G63</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3937,7 +3937,7 @@
         <v>1150</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1155</v>
+        <v>1250</v>
       </c>
       <c r="I63" s="8">
         <f>(H63-G63)/G63</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3959,6 +3959,59 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>铁</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Fe-65%</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Mongolrostsvetmet SOE /Erdenes Critical Minerals SOE/</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>46303.45833333334</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>1 批量/3300吨/</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="8">
+        <f>(H64-G64)/G64</f>
+        <v/>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>2027年10月</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>二连浩特铁路站</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,9 +17,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -66,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -77,19 +77,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -552,7 +546,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="4" t="n">
         <v>46261.41666666666</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -571,7 +565,7 @@
       <c r="H2" s="2" t="n">
         <v>1340</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="5">
         <f>(H2-G2)/G2</f>
         <v/>
       </c>
@@ -608,7 +602,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="4" t="n">
         <v>46261.41666666666</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -627,7 +621,7 @@
       <c r="H3" s="6" t="n">
         <v>190.5</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="5">
         <f>(H3-G3)/G3</f>
         <v/>
       </c>
@@ -663,7 +657,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="4" t="n">
         <v>46262.41666666666</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -682,7 +676,7 @@
       <c r="H4" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="5">
         <f>(H4-G4)/G4</f>
         <v/>
       </c>
@@ -719,7 +713,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="4" t="n">
         <v>46262.41666666666</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -738,7 +732,7 @@
       <c r="H5" s="6" t="n">
         <v>198.5</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="5">
         <f>(H5-G5)/G5</f>
         <v/>
       </c>
@@ -774,7 +768,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="4" t="n">
         <v>46262.5</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -793,7 +787,7 @@
       <c r="H6" s="6" t="n">
         <v>194.5</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="5">
         <f>(H6-G6)/G6</f>
         <v/>
       </c>
@@ -829,7 +823,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="4" t="n">
         <v>46265.41666666666</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -848,7 +842,7 @@
       <c r="H7" s="2" t="n">
         <v>1515</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="5">
         <f>(H7-G7)/G7</f>
         <v/>
       </c>
@@ -885,7 +879,7 @@
           <t>坎加德勘探 有限责任公司</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="4" t="n">
         <v>46266.41666666666</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -904,7 +898,7 @@
       <c r="H8" s="2" t="n">
         <v>1205</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="5">
         <f>(H8-G8)/G8</f>
         <v/>
       </c>
@@ -941,7 +935,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="4" t="n">
         <v>46267.41666666666</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -960,7 +954,7 @@
       <c r="H9" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="5">
         <f>(H9-G9)/G9</f>
         <v/>
       </c>
@@ -997,7 +991,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="4" t="n">
         <v>46267.45833333334</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1016,7 +1010,7 @@
       <c r="H10" s="6" t="n">
         <v>211.5</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="5">
         <f>(H10-G10)/G10</f>
         <v/>
       </c>
@@ -1052,7 +1046,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="4" t="n">
         <v>46267.58333333334</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1071,7 +1065,7 @@
       <c r="H11" s="6" t="n">
         <v>212.5</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="5">
         <f>(H11-G11)/G11</f>
         <v/>
       </c>
@@ -1107,7 +1101,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="4" t="n">
         <v>46268.41666666666</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1126,7 +1120,7 @@
       <c r="H12" s="6" t="n">
         <v>171.4</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="5">
         <f>(H12-G12)/G12</f>
         <v/>
       </c>
@@ -1163,7 +1157,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="4" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1182,7 +1176,7 @@
       <c r="H13" s="6" t="n">
         <v>210.5</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="5">
         <f>(H13-G13)/G13</f>
         <v/>
       </c>
@@ -1218,7 +1212,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="4" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1237,7 +1231,7 @@
       <c r="H14" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="5">
         <f>(H14-G14)/G14</f>
         <v/>
       </c>
@@ -1274,7 +1268,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="4" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1293,7 +1287,7 @@
       <c r="H15" s="2" t="n">
         <v>1445</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="5">
         <f>(H15-G15)/G15</f>
         <v/>
       </c>
@@ -1330,7 +1324,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="4" t="n">
         <v>46269.58333333334</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1349,7 +1343,7 @@
       <c r="H16" s="6" t="n">
         <v>208.5</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="5">
         <f>(H16-G16)/G16</f>
         <v/>
       </c>
@@ -1385,7 +1379,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="4" t="n">
         <v>46272.41666666666</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1404,7 +1398,7 @@
       <c r="H17" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="5">
         <f>(H17-G17)/G17</f>
         <v/>
       </c>
@@ -1441,7 +1435,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="4" t="n">
         <v>46272.41666666666</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1460,7 +1454,7 @@
       <c r="H18" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="5">
         <f>(H18-G18)/G18</f>
         <v/>
       </c>
@@ -1497,7 +1491,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="4" t="n">
         <v>46272.5</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1516,7 +1510,7 @@
       <c r="H19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="5">
         <f>(H19-G19)/G19</f>
         <v/>
       </c>
@@ -1553,7 +1547,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="4" t="n">
         <v>46273.41666666666</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1572,7 +1566,7 @@
       <c r="H20" s="6" t="n">
         <v>193.5</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="5">
         <f>(H20-G20)/G20</f>
         <v/>
       </c>
@@ -1609,7 +1603,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="4" t="n">
         <v>46274.41666666666</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1628,7 +1622,7 @@
       <c r="H21" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="5">
         <f>(H21-G21)/G21</f>
         <v/>
       </c>
@@ -1665,7 +1659,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="4" t="n">
         <v>46274.41666666666</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1684,7 +1678,7 @@
       <c r="H22" s="2" t="n">
         <v>1435</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="5">
         <f>(H22-G22)/G22</f>
         <v/>
       </c>
@@ -1721,7 +1715,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="4" t="n">
         <v>46274.66666666666</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1740,7 +1734,7 @@
       <c r="H23" s="6" t="n">
         <v>187.5</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="5">
         <f>(H23-G23)/G23</f>
         <v/>
       </c>
@@ -1777,7 +1771,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="4" t="n">
         <v>46275.45833333334</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1796,7 +1790,7 @@
       <c r="H24" s="6" t="n">
         <v>120.5</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="5">
         <f>(H24-G24)/G24</f>
         <v/>
       </c>
@@ -1832,7 +1826,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="4" t="n">
         <v>46276.41666666666</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1851,7 +1845,7 @@
       <c r="H25" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="5">
         <f>(H25-G25)/G25</f>
         <v/>
       </c>
@@ -1887,7 +1881,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="4" t="n">
         <v>46276.41666666666</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1906,7 +1900,7 @@
       <c r="H26" s="2" t="n">
         <v>1445</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="5">
         <f>(H26-G26)/G26</f>
         <v/>
       </c>
@@ -1942,7 +1936,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="4" t="n">
         <v>46276.45833333334</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1961,7 +1955,7 @@
       <c r="H27" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="5">
         <f>(H27-G27)/G27</f>
         <v/>
       </c>
@@ -1997,7 +1991,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="4" t="n">
         <v>46276.58333333334</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2016,7 +2010,7 @@
       <c r="H28" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="5">
         <f>(H28-G28)/G28</f>
         <v/>
       </c>
@@ -2052,7 +2046,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="4" t="n">
         <v>46276.625</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2071,7 +2065,7 @@
       <c r="H29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="5">
         <f>(H29-G29)/G29</f>
         <v/>
       </c>
@@ -2107,7 +2101,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="4" t="n">
         <v>46279.41666666666</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2126,7 +2120,7 @@
       <c r="H30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="5">
         <f>(H30-G30)/G30</f>
         <v/>
       </c>
@@ -2162,7 +2156,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="4" t="n">
         <v>46279.41666666666</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2181,7 +2175,7 @@
       <c r="H31" s="2" t="n">
         <v>1420</v>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="5">
         <f>(H31-G31)/G31</f>
         <v/>
       </c>
@@ -2217,7 +2211,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="4" t="n">
         <v>46279.45833333334</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2236,7 +2230,7 @@
       <c r="H32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="5">
         <f>(H32-G32)/G32</f>
         <v/>
       </c>
@@ -2272,7 +2266,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="4" t="n">
         <v>46279.58333333334</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2291,7 +2285,7 @@
       <c r="H33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="5">
         <f>(H33-G33)/G33</f>
         <v/>
       </c>
@@ -2327,7 +2321,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="4" t="n">
         <v>46279.625</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2346,7 +2340,7 @@
       <c r="H34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="5">
         <f>(H34-G34)/G34</f>
         <v/>
       </c>
@@ -2382,7 +2376,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D35" s="4" t="n">
         <v>46280.41666666666</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2401,7 +2395,7 @@
       <c r="H35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="8">
+      <c r="I35" s="5">
         <f>(H35-G35)/G35</f>
         <v/>
       </c>
@@ -2437,7 +2431,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="4" t="n">
         <v>46280.58333333334</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2456,7 +2450,7 @@
       <c r="H36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="8">
+      <c r="I36" s="5">
         <f>(H36-G36)/G36</f>
         <v/>
       </c>
@@ -2492,7 +2486,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="D37" s="4" t="n">
         <v>46281.41666666666</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2511,7 +2505,7 @@
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="8">
+      <c r="I37" s="5">
         <f>(H37-G37)/G37</f>
         <v/>
       </c>
@@ -2547,7 +2541,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="4" t="n">
         <v>46281.41666666666</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2566,7 +2560,7 @@
       <c r="H38" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I38" s="8">
+      <c r="I38" s="5">
         <f>(H38-G38)/G38</f>
         <v/>
       </c>
@@ -2602,7 +2596,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="D39" s="4" t="n">
         <v>46281.58333333334</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2621,7 +2615,7 @@
       <c r="H39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="8">
+      <c r="I39" s="5">
         <f>(H39-G39)/G39</f>
         <v/>
       </c>
@@ -2657,7 +2651,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="4" t="n">
         <v>46282.41666666666</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2676,7 +2670,7 @@
       <c r="H40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="8">
+      <c r="I40" s="5">
         <f>(H40-G40)/G40</f>
         <v/>
       </c>
@@ -2712,7 +2706,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D41" s="4" t="n">
         <v>46282.58333333334</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2731,7 +2725,7 @@
       <c r="H41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="8">
+      <c r="I41" s="5">
         <f>(H41-G41)/G41</f>
         <v/>
       </c>
@@ -2767,7 +2761,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D42" s="4" t="n">
         <v>46283.41666666666</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2786,7 +2780,7 @@
       <c r="H42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="8">
+      <c r="I42" s="5">
         <f>(H42-G42)/G42</f>
         <v/>
       </c>
@@ -2822,7 +2816,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D43" s="7" t="n">
+      <c r="D43" s="4" t="n">
         <v>46283.41666666666</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2841,7 +2835,7 @@
       <c r="H43" s="2" t="n">
         <v>1255</v>
       </c>
-      <c r="I43" s="8">
+      <c r="I43" s="5">
         <f>(H43-G43)/G43</f>
         <v/>
       </c>
@@ -2877,7 +2871,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="D44" s="4" t="n">
         <v>46283.58333333334</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2896,7 +2890,7 @@
       <c r="H44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="8">
+      <c r="I44" s="5">
         <f>(H44-G44)/G44</f>
         <v/>
       </c>
@@ -2932,7 +2926,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="D45" s="4" t="n">
         <v>46286.41666666666</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2951,7 +2945,7 @@
       <c r="H45" s="2" t="n">
         <v>1295</v>
       </c>
-      <c r="I45" s="8">
+      <c r="I45" s="5">
         <f>(H45-G45)/G45</f>
         <v/>
       </c>
@@ -2987,7 +2981,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="D46" s="4" t="n">
         <v>46286.41666666666</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -3006,7 +3000,7 @@
       <c r="H46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="8">
+      <c r="I46" s="5">
         <f>(H46-G46)/G46</f>
         <v/>
       </c>
@@ -3042,7 +3036,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D47" s="7" t="n">
+      <c r="D47" s="4" t="n">
         <v>46286.58333333334</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -3061,7 +3055,7 @@
       <c r="H47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="8">
+      <c r="I47" s="5">
         <f>(H47-G47)/G47</f>
         <v/>
       </c>
@@ -3097,7 +3091,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D48" s="7" t="n">
+      <c r="D48" s="4" t="n">
         <v>46287.41666666666</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -3116,7 +3110,7 @@
       <c r="H48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="8">
+      <c r="I48" s="5">
         <f>(H48-G48)/G48</f>
         <v/>
       </c>
@@ -3152,7 +3146,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D49" s="7" t="n">
+      <c r="D49" s="4" t="n">
         <v>46287.58333333334</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -3171,7 +3165,7 @@
       <c r="H49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I49" s="8">
+      <c r="I49" s="5">
         <f>(H49-G49)/G49</f>
         <v/>
       </c>
@@ -3207,7 +3201,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D50" s="4" t="n">
         <v>46288.41666666666</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -3226,7 +3220,7 @@
       <c r="H50" s="2" t="n">
         <v>1290</v>
       </c>
-      <c r="I50" s="8">
+      <c r="I50" s="5">
         <f>(H50-G50)/G50</f>
         <v/>
       </c>
@@ -3262,7 +3256,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D51" s="7" t="n">
+      <c r="D51" s="4" t="n">
         <v>46288.41666666666</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -3281,7 +3275,7 @@
       <c r="H51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="8">
+      <c r="I51" s="5">
         <f>(H51-G51)/G51</f>
         <v/>
       </c>
@@ -3317,7 +3311,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D52" s="7" t="n">
+      <c r="D52" s="4" t="n">
         <v>46288.58333333334</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -3336,7 +3330,7 @@
       <c r="H52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="8">
+      <c r="I52" s="5">
         <f>(H52-G52)/G52</f>
         <v/>
       </c>
@@ -3372,7 +3366,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D53" s="7" t="n">
+      <c r="D53" s="4" t="n">
         <v>46290.41666666666</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -3391,7 +3385,7 @@
       <c r="H53" s="2" t="n">
         <v>1285</v>
       </c>
-      <c r="I53" s="8">
+      <c r="I53" s="5">
         <f>(H53-G53)/G53</f>
         <v/>
       </c>
@@ -3427,7 +3421,7 @@
           <t>额尔登特矿业公司国资企业</t>
         </is>
       </c>
-      <c r="D54" s="7" t="n">
+      <c r="D54" s="4" t="n">
         <v>46290.625</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -3440,13 +3434,13 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G54" s="6" t="n">
         <v>3318.59</v>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="H54" s="6" t="n">
         <v>3613.59</v>
       </c>
-      <c r="I54" s="8">
+      <c r="I54" s="5">
         <f>(H54-G54)/G54</f>
         <v/>
       </c>
@@ -3482,7 +3476,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D55" s="7" t="n">
+      <c r="D55" s="4" t="n">
         <v>46293.41666666666</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -3501,7 +3495,7 @@
       <c r="H55" s="2" t="n">
         <v>1260</v>
       </c>
-      <c r="I55" s="8">
+      <c r="I55" s="5">
         <f>(H55-G55)/G55</f>
         <v/>
       </c>
@@ -3537,7 +3531,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D56" s="7" t="n">
+      <c r="D56" s="4" t="n">
         <v>46295.41666666666</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -3556,7 +3550,7 @@
       <c r="H56" s="2" t="n">
         <v>1265</v>
       </c>
-      <c r="I56" s="8">
+      <c r="I56" s="5">
         <f>(H56-G56)/G56</f>
         <v/>
       </c>
@@ -3592,7 +3586,7 @@
           <t>坎加德勘探 有限责任公司</t>
         </is>
       </c>
-      <c r="D57" s="7" t="n">
+      <c r="D57" s="4" t="n">
         <v>46296.58333333334</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3611,7 +3605,7 @@
       <c r="H57" s="2" t="n">
         <v>540</v>
       </c>
-      <c r="I57" s="8">
+      <c r="I57" s="5">
         <f>(H57-G57)/G57</f>
         <v/>
       </c>
@@ -3647,7 +3641,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D58" s="7" t="n">
+      <c r="D58" s="4" t="n">
         <v>46297.41666666666</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -3666,7 +3660,7 @@
       <c r="H58" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="I58" s="8">
+      <c r="I58" s="5">
         <f>(H58-G58)/G58</f>
         <v/>
       </c>
@@ -3702,7 +3696,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D59" s="7" t="n">
+      <c r="D59" s="4" t="n">
         <v>46297.41666666666</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -3721,7 +3715,7 @@
       <c r="H59" s="2" t="n">
         <v>1265</v>
       </c>
-      <c r="I59" s="8">
+      <c r="I59" s="5">
         <f>(H59-G59)/G59</f>
         <v/>
       </c>
@@ -3757,7 +3751,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D60" s="7" t="n">
+      <c r="D60" s="4" t="n">
         <v>46300.41666666666</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3774,7 +3768,7 @@
         <v>1150</v>
       </c>
       <c r="H60" s="2" t="n"/>
-      <c r="I60" s="8">
+      <c r="I60" s="5">
         <f>(H60-G60)/G60</f>
         <v/>
       </c>
@@ -3810,7 +3804,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D61" s="7" t="n">
+      <c r="D61" s="4" t="n">
         <v>46301.41666666666</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -3829,7 +3823,7 @@
       <c r="H61" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="I61" s="8">
+      <c r="I61" s="5">
         <f>(H61-G61)/G61</f>
         <v/>
       </c>
@@ -3852,163 +3846,55 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>铁</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Fe-65%</t>
+          <t>洗精主焦煤</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Mongolrostsvetmet SOE /Erdenes Critical Minerals SOE/</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>46301.45833333334</v>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>46302.41666666666</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>1 批量/3300吨/</t>
+          <t>2 批量/12800吨/</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>85</v>
+        <v>1150</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="I62" s="8">
+        <v>1250</v>
+      </c>
+      <c r="I62" s="5">
         <f>(H62-G62)/G62</f>
         <v/>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>2027年10月</t>
+          <t>2027年2月04日（最后供货日） DAP甘其毛都口岸</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>二连浩特铁路站</t>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>铁路</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>洗精主焦煤</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>能源资源有限责任公司</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="n">
-        <v>46302.41666666666</v>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>2 批量/12800吨/</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>1150</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="I63" s="8">
-        <f>(H63-G63)/G63</f>
-        <v/>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>2027年2月04日（最后供货日） DAP甘其毛都口岸</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>买方指定的甘其毛都口岸海关监管区</t>
-        </is>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
           <t>公路运输</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>铁</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Fe-65%</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Mongolrostsvetmet SOE /Erdenes Critical Minerals SOE/</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="n">
-        <v>46303.45833333334</v>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>1 批量/3300吨/</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="H64" s="2" t="n"/>
-      <c r="I64" s="8">
-        <f>(H64-G64)/G64</f>
-        <v/>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>2027年10月</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>二连浩特铁路站</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>铁路</t>
         </is>
       </c>
     </row>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -66,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -77,13 +76,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -546,7 +551,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="7" t="n">
         <v>46261.41666666666</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -565,7 +570,7 @@
       <c r="H2" s="2" t="n">
         <v>1340</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="8">
         <f>(H2-G2)/G2</f>
         <v/>
       </c>
@@ -602,7 +607,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="7" t="n">
         <v>46261.41666666666</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -621,7 +626,7 @@
       <c r="H3" s="6" t="n">
         <v>190.5</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="8">
         <f>(H3-G3)/G3</f>
         <v/>
       </c>
@@ -657,7 +662,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="7" t="n">
         <v>46262.41666666666</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -676,7 +681,7 @@
       <c r="H4" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="8">
         <f>(H4-G4)/G4</f>
         <v/>
       </c>
@@ -713,7 +718,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="7" t="n">
         <v>46262.41666666666</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -732,7 +737,7 @@
       <c r="H5" s="6" t="n">
         <v>198.5</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="8">
         <f>(H5-G5)/G5</f>
         <v/>
       </c>
@@ -768,7 +773,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="7" t="n">
         <v>46262.5</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -787,7 +792,7 @@
       <c r="H6" s="6" t="n">
         <v>194.5</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="8">
         <f>(H6-G6)/G6</f>
         <v/>
       </c>
@@ -823,7 +828,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="7" t="n">
         <v>46265.41666666666</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -842,7 +847,7 @@
       <c r="H7" s="2" t="n">
         <v>1515</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="8">
         <f>(H7-G7)/G7</f>
         <v/>
       </c>
@@ -879,7 +884,7 @@
           <t>坎加德勘探 有限责任公司</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="7" t="n">
         <v>46266.41666666666</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -898,7 +903,7 @@
       <c r="H8" s="2" t="n">
         <v>1205</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="8">
         <f>(H8-G8)/G8</f>
         <v/>
       </c>
@@ -935,7 +940,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="7" t="n">
         <v>46267.41666666666</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -954,7 +959,7 @@
       <c r="H9" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="8">
         <f>(H9-G9)/G9</f>
         <v/>
       </c>
@@ -991,7 +996,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="7" t="n">
         <v>46267.45833333334</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1010,7 +1015,7 @@
       <c r="H10" s="6" t="n">
         <v>211.5</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="8">
         <f>(H10-G10)/G10</f>
         <v/>
       </c>
@@ -1046,7 +1051,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="7" t="n">
         <v>46267.58333333334</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1065,7 +1070,7 @@
       <c r="H11" s="6" t="n">
         <v>212.5</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="8">
         <f>(H11-G11)/G11</f>
         <v/>
       </c>
@@ -1101,7 +1106,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="7" t="n">
         <v>46268.41666666666</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1120,7 +1125,7 @@
       <c r="H12" s="6" t="n">
         <v>171.4</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="8">
         <f>(H12-G12)/G12</f>
         <v/>
       </c>
@@ -1157,7 +1162,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="7" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1176,7 +1181,7 @@
       <c r="H13" s="6" t="n">
         <v>210.5</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="8">
         <f>(H13-G13)/G13</f>
         <v/>
       </c>
@@ -1212,7 +1217,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="7" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1231,7 +1236,7 @@
       <c r="H14" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="8">
         <f>(H14-G14)/G14</f>
         <v/>
       </c>
@@ -1268,7 +1273,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="7" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1287,7 +1292,7 @@
       <c r="H15" s="2" t="n">
         <v>1445</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="8">
         <f>(H15-G15)/G15</f>
         <v/>
       </c>
@@ -1324,7 +1329,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="7" t="n">
         <v>46269.58333333334</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1343,7 +1348,7 @@
       <c r="H16" s="6" t="n">
         <v>208.5</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="8">
         <f>(H16-G16)/G16</f>
         <v/>
       </c>
@@ -1379,7 +1384,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="7" t="n">
         <v>46272.41666666666</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1398,7 +1403,7 @@
       <c r="H17" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="8">
         <f>(H17-G17)/G17</f>
         <v/>
       </c>
@@ -1435,7 +1440,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="7" t="n">
         <v>46272.41666666666</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1454,7 +1459,7 @@
       <c r="H18" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="8">
         <f>(H18-G18)/G18</f>
         <v/>
       </c>
@@ -1491,7 +1496,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="7" t="n">
         <v>46272.5</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1510,7 +1515,7 @@
       <c r="H19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="8">
         <f>(H19-G19)/G19</f>
         <v/>
       </c>
@@ -1547,7 +1552,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="7" t="n">
         <v>46273.41666666666</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1566,7 +1571,7 @@
       <c r="H20" s="6" t="n">
         <v>193.5</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="8">
         <f>(H20-G20)/G20</f>
         <v/>
       </c>
@@ -1603,7 +1608,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="7" t="n">
         <v>46274.41666666666</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1622,7 +1627,7 @@
       <c r="H21" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="8">
         <f>(H21-G21)/G21</f>
         <v/>
       </c>
@@ -1659,7 +1664,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="7" t="n">
         <v>46274.41666666666</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1678,7 +1683,7 @@
       <c r="H22" s="2" t="n">
         <v>1435</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="8">
         <f>(H22-G22)/G22</f>
         <v/>
       </c>
@@ -1715,7 +1720,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="7" t="n">
         <v>46274.66666666666</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1734,7 +1739,7 @@
       <c r="H23" s="6" t="n">
         <v>187.5</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="8">
         <f>(H23-G23)/G23</f>
         <v/>
       </c>
@@ -1771,7 +1776,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="7" t="n">
         <v>46275.45833333334</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1790,7 +1795,7 @@
       <c r="H24" s="6" t="n">
         <v>120.5</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="8">
         <f>(H24-G24)/G24</f>
         <v/>
       </c>
@@ -1826,7 +1831,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="7" t="n">
         <v>46276.41666666666</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1845,7 +1850,7 @@
       <c r="H25" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="8">
         <f>(H25-G25)/G25</f>
         <v/>
       </c>
@@ -1881,7 +1886,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="7" t="n">
         <v>46276.41666666666</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1900,7 +1905,7 @@
       <c r="H26" s="2" t="n">
         <v>1445</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="8">
         <f>(H26-G26)/G26</f>
         <v/>
       </c>
@@ -1936,7 +1941,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="7" t="n">
         <v>46276.45833333334</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1955,7 +1960,7 @@
       <c r="H27" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="8">
         <f>(H27-G27)/G27</f>
         <v/>
       </c>
@@ -1991,7 +1996,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="7" t="n">
         <v>46276.58333333334</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2010,7 +2015,7 @@
       <c r="H28" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="8">
         <f>(H28-G28)/G28</f>
         <v/>
       </c>
@@ -2046,7 +2051,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="7" t="n">
         <v>46276.625</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2065,7 +2070,7 @@
       <c r="H29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="8">
         <f>(H29-G29)/G29</f>
         <v/>
       </c>
@@ -2101,7 +2106,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="7" t="n">
         <v>46279.41666666666</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2120,7 +2125,7 @@
       <c r="H30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="8">
         <f>(H30-G30)/G30</f>
         <v/>
       </c>
@@ -2156,7 +2161,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="7" t="n">
         <v>46279.41666666666</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2175,7 +2180,7 @@
       <c r="H31" s="2" t="n">
         <v>1420</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="8">
         <f>(H31-G31)/G31</f>
         <v/>
       </c>
@@ -2211,7 +2216,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="7" t="n">
         <v>46279.45833333334</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2230,7 +2235,7 @@
       <c r="H32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="8">
         <f>(H32-G32)/G32</f>
         <v/>
       </c>
@@ -2266,7 +2271,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="7" t="n">
         <v>46279.58333333334</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2285,7 +2290,7 @@
       <c r="H33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="8">
         <f>(H33-G33)/G33</f>
         <v/>
       </c>
@@ -2321,7 +2326,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="7" t="n">
         <v>46279.625</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2340,7 +2345,7 @@
       <c r="H34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="8">
         <f>(H34-G34)/G34</f>
         <v/>
       </c>
@@ -2376,7 +2381,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="7" t="n">
         <v>46280.41666666666</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2395,7 +2400,7 @@
       <c r="H35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="8">
         <f>(H35-G35)/G35</f>
         <v/>
       </c>
@@ -2431,7 +2436,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="7" t="n">
         <v>46280.58333333334</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2450,7 +2455,7 @@
       <c r="H36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="8">
         <f>(H36-G36)/G36</f>
         <v/>
       </c>
@@ -2486,7 +2491,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="7" t="n">
         <v>46281.41666666666</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2505,7 +2510,7 @@
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="8">
         <f>(H37-G37)/G37</f>
         <v/>
       </c>
@@ -2541,7 +2546,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="7" t="n">
         <v>46281.41666666666</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2560,7 +2565,7 @@
       <c r="H38" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="8">
         <f>(H38-G38)/G38</f>
         <v/>
       </c>
@@ -2596,7 +2601,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="7" t="n">
         <v>46281.58333333334</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2615,7 +2620,7 @@
       <c r="H39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="8">
         <f>(H39-G39)/G39</f>
         <v/>
       </c>
@@ -2651,7 +2656,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="7" t="n">
         <v>46282.41666666666</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2670,7 +2675,7 @@
       <c r="H40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="8">
         <f>(H40-G40)/G40</f>
         <v/>
       </c>
@@ -2706,7 +2711,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="7" t="n">
         <v>46282.58333333334</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2725,7 +2730,7 @@
       <c r="H41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="8">
         <f>(H41-G41)/G41</f>
         <v/>
       </c>
@@ -2761,7 +2766,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="7" t="n">
         <v>46283.41666666666</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2780,7 +2785,7 @@
       <c r="H42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="8">
         <f>(H42-G42)/G42</f>
         <v/>
       </c>
@@ -2816,7 +2821,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="7" t="n">
         <v>46283.41666666666</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2835,7 +2840,7 @@
       <c r="H43" s="2" t="n">
         <v>1255</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="8">
         <f>(H43-G43)/G43</f>
         <v/>
       </c>
@@ -2871,7 +2876,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="7" t="n">
         <v>46283.58333333334</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2890,7 +2895,7 @@
       <c r="H44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="8">
         <f>(H44-G44)/G44</f>
         <v/>
       </c>
@@ -2926,7 +2931,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="7" t="n">
         <v>46286.41666666666</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2945,7 +2950,7 @@
       <c r="H45" s="2" t="n">
         <v>1295</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="8">
         <f>(H45-G45)/G45</f>
         <v/>
       </c>
@@ -2981,7 +2986,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="7" t="n">
         <v>46286.41666666666</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -3000,7 +3005,7 @@
       <c r="H46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="8">
         <f>(H46-G46)/G46</f>
         <v/>
       </c>
@@ -3036,7 +3041,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="7" t="n">
         <v>46286.58333333334</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -3055,7 +3060,7 @@
       <c r="H47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="8">
         <f>(H47-G47)/G47</f>
         <v/>
       </c>
@@ -3091,7 +3096,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="7" t="n">
         <v>46287.41666666666</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -3110,7 +3115,7 @@
       <c r="H48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="8">
         <f>(H48-G48)/G48</f>
         <v/>
       </c>
@@ -3146,7 +3151,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="7" t="n">
         <v>46287.58333333334</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -3165,7 +3170,7 @@
       <c r="H49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I49" s="8">
         <f>(H49-G49)/G49</f>
         <v/>
       </c>
@@ -3201,7 +3206,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="7" t="n">
         <v>46288.41666666666</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -3220,7 +3225,7 @@
       <c r="H50" s="2" t="n">
         <v>1290</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I50" s="8">
         <f>(H50-G50)/G50</f>
         <v/>
       </c>
@@ -3256,7 +3261,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="7" t="n">
         <v>46288.41666666666</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -3275,7 +3280,7 @@
       <c r="H51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I51" s="8">
         <f>(H51-G51)/G51</f>
         <v/>
       </c>
@@ -3311,7 +3316,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="7" t="n">
         <v>46288.58333333334</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -3330,7 +3335,7 @@
       <c r="H52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I52" s="8">
         <f>(H52-G52)/G52</f>
         <v/>
       </c>
@@ -3366,7 +3371,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="7" t="n">
         <v>46290.41666666666</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -3385,7 +3390,7 @@
       <c r="H53" s="2" t="n">
         <v>1285</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I53" s="8">
         <f>(H53-G53)/G53</f>
         <v/>
       </c>
@@ -3421,7 +3426,7 @@
           <t>额尔登特矿业公司国资企业</t>
         </is>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="7" t="n">
         <v>46290.625</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -3440,7 +3445,7 @@
       <c r="H54" s="6" t="n">
         <v>3613.59</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I54" s="8">
         <f>(H54-G54)/G54</f>
         <v/>
       </c>
@@ -3476,7 +3481,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="7" t="n">
         <v>46293.41666666666</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -3495,7 +3500,7 @@
       <c r="H55" s="2" t="n">
         <v>1260</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I55" s="8">
         <f>(H55-G55)/G55</f>
         <v/>
       </c>
@@ -3531,7 +3536,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="7" t="n">
         <v>46295.41666666666</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -3550,7 +3555,7 @@
       <c r="H56" s="2" t="n">
         <v>1265</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I56" s="8">
         <f>(H56-G56)/G56</f>
         <v/>
       </c>
@@ -3586,7 +3591,7 @@
           <t>坎加德勘探 有限责任公司</t>
         </is>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="7" t="n">
         <v>46296.58333333334</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3605,7 +3610,7 @@
       <c r="H57" s="2" t="n">
         <v>540</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I57" s="8">
         <f>(H57-G57)/G57</f>
         <v/>
       </c>
@@ -3641,7 +3646,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="7" t="n">
         <v>46297.41666666666</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -3660,7 +3665,7 @@
       <c r="H58" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="I58" s="5">
+      <c r="I58" s="8">
         <f>(H58-G58)/G58</f>
         <v/>
       </c>
@@ -3696,7 +3701,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="7" t="n">
         <v>46297.41666666666</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -3715,7 +3720,7 @@
       <c r="H59" s="2" t="n">
         <v>1265</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="8">
         <f>(H59-G59)/G59</f>
         <v/>
       </c>
@@ -3751,7 +3756,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="7" t="n">
         <v>46300.41666666666</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3768,7 +3773,7 @@
         <v>1150</v>
       </c>
       <c r="H60" s="2" t="n"/>
-      <c r="I60" s="5">
+      <c r="I60" s="8">
         <f>(H60-G60)/G60</f>
         <v/>
       </c>
@@ -3804,7 +3809,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="7" t="n">
         <v>46301.41666666666</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -3823,7 +3828,7 @@
       <c r="H61" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="I61" s="5">
+      <c r="I61" s="8">
         <f>(H61-G61)/G61</f>
         <v/>
       </c>
@@ -3859,7 +3864,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="7" t="n">
         <v>46302.41666666666</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3878,7 +3883,7 @@
       <c r="H62" s="2" t="n">
         <v>1250</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I62" s="8">
         <f>(H62-G62)/G62</f>
         <v/>
       </c>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -456,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3903,6 +3904,59 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>46304.41666666666</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="8">
+        <f>(H63-G63)/G63</f>
+        <v/>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月06日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3936,7 +3936,9 @@
       <c r="G63" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H63" s="2" t="n"/>
+      <c r="H63" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I63" s="8">
         <f>(H63-G63)/G63</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3937,7 +3937,7 @@
         <v>1150</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1150</v>
+        <v>1260</v>
       </c>
       <c r="I63" s="8">
         <f>(H63-G63)/G63</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -456,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3958,6 +3959,59 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>46307.41666666666</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="8">
+        <f>(H64-G64)/G64</f>
+        <v/>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月09日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3991,7 +3991,9 @@
       <c r="G64" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H64" s="2" t="n"/>
+      <c r="H64" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I64" s="8">
         <f>(H64-G64)/G64</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3992,7 +3992,7 @@
         <v>1150</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1150</v>
+        <v>1260</v>
       </c>
       <c r="I64" s="8">
         <f>(H64-G64)/G64</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -3991,9 +3991,7 @@
       <c r="G64" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H64" s="2" t="n">
-        <v>1260</v>
-      </c>
+      <c r="H64" s="2" t="n"/>
       <c r="I64" s="8">
         <f>(H64-G64)/G64</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -65,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -76,19 +77,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -551,7 +546,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="4" t="n">
         <v>46261.41666666666</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -570,7 +565,7 @@
       <c r="H2" s="2" t="n">
         <v>1340</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="5">
         <f>(H2-G2)/G2</f>
         <v/>
       </c>
@@ -607,7 +602,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="4" t="n">
         <v>46261.41666666666</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -626,7 +621,7 @@
       <c r="H3" s="6" t="n">
         <v>190.5</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="5">
         <f>(H3-G3)/G3</f>
         <v/>
       </c>
@@ -662,7 +657,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="4" t="n">
         <v>46262.41666666666</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -681,7 +676,7 @@
       <c r="H4" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="5">
         <f>(H4-G4)/G4</f>
         <v/>
       </c>
@@ -718,7 +713,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="4" t="n">
         <v>46262.41666666666</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -737,7 +732,7 @@
       <c r="H5" s="6" t="n">
         <v>198.5</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="5">
         <f>(H5-G5)/G5</f>
         <v/>
       </c>
@@ -773,7 +768,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="4" t="n">
         <v>46262.5</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -792,7 +787,7 @@
       <c r="H6" s="6" t="n">
         <v>194.5</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="5">
         <f>(H6-G6)/G6</f>
         <v/>
       </c>
@@ -828,7 +823,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="4" t="n">
         <v>46265.41666666666</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -847,7 +842,7 @@
       <c r="H7" s="2" t="n">
         <v>1515</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="5">
         <f>(H7-G7)/G7</f>
         <v/>
       </c>
@@ -884,7 +879,7 @@
           <t>坎加德勘探 有限责任公司</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="4" t="n">
         <v>46266.41666666666</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -903,7 +898,7 @@
       <c r="H8" s="2" t="n">
         <v>1205</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="5">
         <f>(H8-G8)/G8</f>
         <v/>
       </c>
@@ -940,7 +935,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="4" t="n">
         <v>46267.41666666666</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -959,7 +954,7 @@
       <c r="H9" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="5">
         <f>(H9-G9)/G9</f>
         <v/>
       </c>
@@ -996,7 +991,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="4" t="n">
         <v>46267.45833333334</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1015,7 +1010,7 @@
       <c r="H10" s="6" t="n">
         <v>211.5</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="5">
         <f>(H10-G10)/G10</f>
         <v/>
       </c>
@@ -1051,7 +1046,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="4" t="n">
         <v>46267.58333333334</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1070,7 +1065,7 @@
       <c r="H11" s="6" t="n">
         <v>212.5</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="5">
         <f>(H11-G11)/G11</f>
         <v/>
       </c>
@@ -1106,7 +1101,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="4" t="n">
         <v>46268.41666666666</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1125,7 +1120,7 @@
       <c r="H12" s="6" t="n">
         <v>171.4</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="5">
         <f>(H12-G12)/G12</f>
         <v/>
       </c>
@@ -1162,7 +1157,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="4" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1181,7 +1176,7 @@
       <c r="H13" s="6" t="n">
         <v>210.5</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="5">
         <f>(H13-G13)/G13</f>
         <v/>
       </c>
@@ -1217,7 +1212,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="4" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1236,7 +1231,7 @@
       <c r="H14" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="5">
         <f>(H14-G14)/G14</f>
         <v/>
       </c>
@@ -1273,7 +1268,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="4" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1292,7 +1287,7 @@
       <c r="H15" s="2" t="n">
         <v>1445</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="5">
         <f>(H15-G15)/G15</f>
         <v/>
       </c>
@@ -1329,7 +1324,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="4" t="n">
         <v>46269.58333333334</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1348,7 +1343,7 @@
       <c r="H16" s="6" t="n">
         <v>208.5</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="5">
         <f>(H16-G16)/G16</f>
         <v/>
       </c>
@@ -1384,7 +1379,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="4" t="n">
         <v>46272.41666666666</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1403,7 +1398,7 @@
       <c r="H17" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="5">
         <f>(H17-G17)/G17</f>
         <v/>
       </c>
@@ -1440,7 +1435,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="4" t="n">
         <v>46272.41666666666</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1459,7 +1454,7 @@
       <c r="H18" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="5">
         <f>(H18-G18)/G18</f>
         <v/>
       </c>
@@ -1496,7 +1491,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="4" t="n">
         <v>46272.5</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1515,7 +1510,7 @@
       <c r="H19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="5">
         <f>(H19-G19)/G19</f>
         <v/>
       </c>
@@ -1552,7 +1547,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="4" t="n">
         <v>46273.41666666666</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1571,7 +1566,7 @@
       <c r="H20" s="6" t="n">
         <v>193.5</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="5">
         <f>(H20-G20)/G20</f>
         <v/>
       </c>
@@ -1608,7 +1603,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="4" t="n">
         <v>46274.41666666666</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1627,7 +1622,7 @@
       <c r="H21" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="5">
         <f>(H21-G21)/G21</f>
         <v/>
       </c>
@@ -1664,7 +1659,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="4" t="n">
         <v>46274.41666666666</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1683,7 +1678,7 @@
       <c r="H22" s="2" t="n">
         <v>1435</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="5">
         <f>(H22-G22)/G22</f>
         <v/>
       </c>
@@ -1720,7 +1715,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="4" t="n">
         <v>46274.66666666666</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1739,7 +1734,7 @@
       <c r="H23" s="6" t="n">
         <v>187.5</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="5">
         <f>(H23-G23)/G23</f>
         <v/>
       </c>
@@ -1776,7 +1771,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="4" t="n">
         <v>46275.45833333334</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1795,7 +1790,7 @@
       <c r="H24" s="6" t="n">
         <v>120.5</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="5">
         <f>(H24-G24)/G24</f>
         <v/>
       </c>
@@ -1831,7 +1826,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="4" t="n">
         <v>46276.41666666666</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1850,7 +1845,7 @@
       <c r="H25" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="5">
         <f>(H25-G25)/G25</f>
         <v/>
       </c>
@@ -1886,7 +1881,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="4" t="n">
         <v>46276.41666666666</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1905,7 +1900,7 @@
       <c r="H26" s="2" t="n">
         <v>1445</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="5">
         <f>(H26-G26)/G26</f>
         <v/>
       </c>
@@ -1941,7 +1936,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="4" t="n">
         <v>46276.45833333334</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1960,7 +1955,7 @@
       <c r="H27" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="5">
         <f>(H27-G27)/G27</f>
         <v/>
       </c>
@@ -1996,7 +1991,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="4" t="n">
         <v>46276.58333333334</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2015,7 +2010,7 @@
       <c r="H28" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="5">
         <f>(H28-G28)/G28</f>
         <v/>
       </c>
@@ -2051,7 +2046,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="4" t="n">
         <v>46276.625</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2070,7 +2065,7 @@
       <c r="H29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="5">
         <f>(H29-G29)/G29</f>
         <v/>
       </c>
@@ -2106,7 +2101,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="4" t="n">
         <v>46279.41666666666</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2125,7 +2120,7 @@
       <c r="H30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="5">
         <f>(H30-G30)/G30</f>
         <v/>
       </c>
@@ -2161,7 +2156,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="4" t="n">
         <v>46279.41666666666</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2180,7 +2175,7 @@
       <c r="H31" s="2" t="n">
         <v>1420</v>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="5">
         <f>(H31-G31)/G31</f>
         <v/>
       </c>
@@ -2216,7 +2211,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="4" t="n">
         <v>46279.45833333334</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2235,7 +2230,7 @@
       <c r="H32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="5">
         <f>(H32-G32)/G32</f>
         <v/>
       </c>
@@ -2271,7 +2266,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="4" t="n">
         <v>46279.58333333334</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2290,7 +2285,7 @@
       <c r="H33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="5">
         <f>(H33-G33)/G33</f>
         <v/>
       </c>
@@ -2326,7 +2321,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="4" t="n">
         <v>46279.625</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2345,7 +2340,7 @@
       <c r="H34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="5">
         <f>(H34-G34)/G34</f>
         <v/>
       </c>
@@ -2381,7 +2376,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D35" s="4" t="n">
         <v>46280.41666666666</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2400,7 +2395,7 @@
       <c r="H35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="8">
+      <c r="I35" s="5">
         <f>(H35-G35)/G35</f>
         <v/>
       </c>
@@ -2436,7 +2431,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="4" t="n">
         <v>46280.58333333334</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2455,7 +2450,7 @@
       <c r="H36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="8">
+      <c r="I36" s="5">
         <f>(H36-G36)/G36</f>
         <v/>
       </c>
@@ -2491,7 +2486,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="D37" s="4" t="n">
         <v>46281.41666666666</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2510,7 +2505,7 @@
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="8">
+      <c r="I37" s="5">
         <f>(H37-G37)/G37</f>
         <v/>
       </c>
@@ -2546,7 +2541,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="4" t="n">
         <v>46281.41666666666</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2565,7 +2560,7 @@
       <c r="H38" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I38" s="8">
+      <c r="I38" s="5">
         <f>(H38-G38)/G38</f>
         <v/>
       </c>
@@ -2601,7 +2596,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="D39" s="4" t="n">
         <v>46281.58333333334</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2620,7 +2615,7 @@
       <c r="H39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="8">
+      <c r="I39" s="5">
         <f>(H39-G39)/G39</f>
         <v/>
       </c>
@@ -2656,7 +2651,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="4" t="n">
         <v>46282.41666666666</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2675,7 +2670,7 @@
       <c r="H40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="8">
+      <c r="I40" s="5">
         <f>(H40-G40)/G40</f>
         <v/>
       </c>
@@ -2711,7 +2706,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D41" s="4" t="n">
         <v>46282.58333333334</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2730,7 +2725,7 @@
       <c r="H41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="8">
+      <c r="I41" s="5">
         <f>(H41-G41)/G41</f>
         <v/>
       </c>
@@ -2766,7 +2761,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D42" s="4" t="n">
         <v>46283.41666666666</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2785,7 +2780,7 @@
       <c r="H42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="8">
+      <c r="I42" s="5">
         <f>(H42-G42)/G42</f>
         <v/>
       </c>
@@ -2821,7 +2816,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D43" s="7" t="n">
+      <c r="D43" s="4" t="n">
         <v>46283.41666666666</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2840,7 +2835,7 @@
       <c r="H43" s="2" t="n">
         <v>1255</v>
       </c>
-      <c r="I43" s="8">
+      <c r="I43" s="5">
         <f>(H43-G43)/G43</f>
         <v/>
       </c>
@@ -2876,7 +2871,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="D44" s="4" t="n">
         <v>46283.58333333334</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2895,7 +2890,7 @@
       <c r="H44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="8">
+      <c r="I44" s="5">
         <f>(H44-G44)/G44</f>
         <v/>
       </c>
@@ -2931,7 +2926,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="D45" s="4" t="n">
         <v>46286.41666666666</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2950,7 +2945,7 @@
       <c r="H45" s="2" t="n">
         <v>1295</v>
       </c>
-      <c r="I45" s="8">
+      <c r="I45" s="5">
         <f>(H45-G45)/G45</f>
         <v/>
       </c>
@@ -2986,7 +2981,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="D46" s="4" t="n">
         <v>46286.41666666666</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -3005,7 +3000,7 @@
       <c r="H46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="8">
+      <c r="I46" s="5">
         <f>(H46-G46)/G46</f>
         <v/>
       </c>
@@ -3041,7 +3036,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D47" s="7" t="n">
+      <c r="D47" s="4" t="n">
         <v>46286.58333333334</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -3060,7 +3055,7 @@
       <c r="H47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="8">
+      <c r="I47" s="5">
         <f>(H47-G47)/G47</f>
         <v/>
       </c>
@@ -3096,7 +3091,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D48" s="7" t="n">
+      <c r="D48" s="4" t="n">
         <v>46287.41666666666</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -3115,7 +3110,7 @@
       <c r="H48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="8">
+      <c r="I48" s="5">
         <f>(H48-G48)/G48</f>
         <v/>
       </c>
@@ -3151,7 +3146,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D49" s="7" t="n">
+      <c r="D49" s="4" t="n">
         <v>46287.58333333334</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -3170,7 +3165,7 @@
       <c r="H49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I49" s="8">
+      <c r="I49" s="5">
         <f>(H49-G49)/G49</f>
         <v/>
       </c>
@@ -3206,7 +3201,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D50" s="4" t="n">
         <v>46288.41666666666</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -3225,7 +3220,7 @@
       <c r="H50" s="2" t="n">
         <v>1290</v>
       </c>
-      <c r="I50" s="8">
+      <c r="I50" s="5">
         <f>(H50-G50)/G50</f>
         <v/>
       </c>
@@ -3261,7 +3256,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D51" s="7" t="n">
+      <c r="D51" s="4" t="n">
         <v>46288.41666666666</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -3280,7 +3275,7 @@
       <c r="H51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="8">
+      <c r="I51" s="5">
         <f>(H51-G51)/G51</f>
         <v/>
       </c>
@@ -3316,7 +3311,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D52" s="7" t="n">
+      <c r="D52" s="4" t="n">
         <v>46288.58333333334</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -3335,7 +3330,7 @@
       <c r="H52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="8">
+      <c r="I52" s="5">
         <f>(H52-G52)/G52</f>
         <v/>
       </c>
@@ -3371,7 +3366,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D53" s="7" t="n">
+      <c r="D53" s="4" t="n">
         <v>46290.41666666666</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -3390,7 +3385,7 @@
       <c r="H53" s="2" t="n">
         <v>1285</v>
       </c>
-      <c r="I53" s="8">
+      <c r="I53" s="5">
         <f>(H53-G53)/G53</f>
         <v/>
       </c>
@@ -3426,7 +3421,7 @@
           <t>额尔登特矿业公司国资企业</t>
         </is>
       </c>
-      <c r="D54" s="7" t="n">
+      <c r="D54" s="4" t="n">
         <v>46290.625</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -3445,7 +3440,7 @@
       <c r="H54" s="6" t="n">
         <v>3613.59</v>
       </c>
-      <c r="I54" s="8">
+      <c r="I54" s="5">
         <f>(H54-G54)/G54</f>
         <v/>
       </c>
@@ -3481,7 +3476,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D55" s="7" t="n">
+      <c r="D55" s="4" t="n">
         <v>46293.41666666666</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -3500,7 +3495,7 @@
       <c r="H55" s="2" t="n">
         <v>1260</v>
       </c>
-      <c r="I55" s="8">
+      <c r="I55" s="5">
         <f>(H55-G55)/G55</f>
         <v/>
       </c>
@@ -3536,7 +3531,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D56" s="7" t="n">
+      <c r="D56" s="4" t="n">
         <v>46295.41666666666</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -3555,7 +3550,7 @@
       <c r="H56" s="2" t="n">
         <v>1265</v>
       </c>
-      <c r="I56" s="8">
+      <c r="I56" s="5">
         <f>(H56-G56)/G56</f>
         <v/>
       </c>
@@ -3591,7 +3586,7 @@
           <t>坎加德勘探 有限责任公司</t>
         </is>
       </c>
-      <c r="D57" s="7" t="n">
+      <c r="D57" s="4" t="n">
         <v>46296.58333333334</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3610,7 +3605,7 @@
       <c r="H57" s="2" t="n">
         <v>540</v>
       </c>
-      <c r="I57" s="8">
+      <c r="I57" s="5">
         <f>(H57-G57)/G57</f>
         <v/>
       </c>
@@ -3646,7 +3641,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D58" s="7" t="n">
+      <c r="D58" s="4" t="n">
         <v>46297.41666666666</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -3665,7 +3660,7 @@
       <c r="H58" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="I58" s="8">
+      <c r="I58" s="5">
         <f>(H58-G58)/G58</f>
         <v/>
       </c>
@@ -3701,7 +3696,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D59" s="7" t="n">
+      <c r="D59" s="4" t="n">
         <v>46297.41666666666</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -3720,7 +3715,7 @@
       <c r="H59" s="2" t="n">
         <v>1265</v>
       </c>
-      <c r="I59" s="8">
+      <c r="I59" s="5">
         <f>(H59-G59)/G59</f>
         <v/>
       </c>
@@ -3756,7 +3751,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D60" s="7" t="n">
+      <c r="D60" s="4" t="n">
         <v>46300.41666666666</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3772,8 +3767,10 @@
       <c r="G60" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H60" s="2" t="n"/>
-      <c r="I60" s="8">
+      <c r="H60" s="2" t="n">
+        <v>1255</v>
+      </c>
+      <c r="I60" s="5">
         <f>(H60-G60)/G60</f>
         <v/>
       </c>
@@ -3809,7 +3806,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D61" s="7" t="n">
+      <c r="D61" s="4" t="n">
         <v>46301.41666666666</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -3828,7 +3825,7 @@
       <c r="H61" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="I61" s="8">
+      <c r="I61" s="5">
         <f>(H61-G61)/G61</f>
         <v/>
       </c>
@@ -3864,7 +3861,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D62" s="7" t="n">
+      <c r="D62" s="4" t="n">
         <v>46302.41666666666</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3883,7 +3880,7 @@
       <c r="H62" s="2" t="n">
         <v>1250</v>
       </c>
-      <c r="I62" s="8">
+      <c r="I62" s="5">
         <f>(H62-G62)/G62</f>
         <v/>
       </c>
@@ -3919,7 +3916,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D63" s="7" t="n">
+      <c r="D63" s="4" t="n">
         <v>46304.41666666666</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -3938,7 +3935,7 @@
       <c r="H63" s="2" t="n">
         <v>1260</v>
       </c>
-      <c r="I63" s="8">
+      <c r="I63" s="5">
         <f>(H63-G63)/G63</f>
         <v/>
       </c>
@@ -3974,7 +3971,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D64" s="7" t="n">
+      <c r="D64" s="4" t="n">
         <v>46307.41666666666</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -3990,8 +3987,10 @@
       <c r="G64" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H64" s="2" t="n"/>
-      <c r="I64" s="8">
+      <c r="H64" s="2" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I64" s="5">
         <f>(H64-G64)/G64</f>
         <v/>
       </c>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -66,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -77,13 +76,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -546,7 +551,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="7" t="n">
         <v>46261.41666666666</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -565,7 +570,7 @@
       <c r="H2" s="2" t="n">
         <v>1340</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="8">
         <f>(H2-G2)/G2</f>
         <v/>
       </c>
@@ -602,7 +607,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="7" t="n">
         <v>46261.41666666666</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -621,7 +626,7 @@
       <c r="H3" s="6" t="n">
         <v>190.5</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="8">
         <f>(H3-G3)/G3</f>
         <v/>
       </c>
@@ -657,7 +662,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="7" t="n">
         <v>46262.41666666666</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -676,7 +681,7 @@
       <c r="H4" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="8">
         <f>(H4-G4)/G4</f>
         <v/>
       </c>
@@ -713,7 +718,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="7" t="n">
         <v>46262.41666666666</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -732,7 +737,7 @@
       <c r="H5" s="6" t="n">
         <v>198.5</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="8">
         <f>(H5-G5)/G5</f>
         <v/>
       </c>
@@ -768,7 +773,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="7" t="n">
         <v>46262.5</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -787,7 +792,7 @@
       <c r="H6" s="6" t="n">
         <v>194.5</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="8">
         <f>(H6-G6)/G6</f>
         <v/>
       </c>
@@ -823,7 +828,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="7" t="n">
         <v>46265.41666666666</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -842,7 +847,7 @@
       <c r="H7" s="2" t="n">
         <v>1515</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="8">
         <f>(H7-G7)/G7</f>
         <v/>
       </c>
@@ -879,7 +884,7 @@
           <t>坎加德勘探 有限责任公司</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="7" t="n">
         <v>46266.41666666666</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -898,7 +903,7 @@
       <c r="H8" s="2" t="n">
         <v>1205</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="8">
         <f>(H8-G8)/G8</f>
         <v/>
       </c>
@@ -935,7 +940,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="7" t="n">
         <v>46267.41666666666</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -954,7 +959,7 @@
       <c r="H9" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="8">
         <f>(H9-G9)/G9</f>
         <v/>
       </c>
@@ -991,7 +996,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="7" t="n">
         <v>46267.45833333334</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1010,7 +1015,7 @@
       <c r="H10" s="6" t="n">
         <v>211.5</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="8">
         <f>(H10-G10)/G10</f>
         <v/>
       </c>
@@ -1046,7 +1051,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="7" t="n">
         <v>46267.58333333334</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1065,7 +1070,7 @@
       <c r="H11" s="6" t="n">
         <v>212.5</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="8">
         <f>(H11-G11)/G11</f>
         <v/>
       </c>
@@ -1101,7 +1106,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="7" t="n">
         <v>46268.41666666666</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1120,7 +1125,7 @@
       <c r="H12" s="6" t="n">
         <v>171.4</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="8">
         <f>(H12-G12)/G12</f>
         <v/>
       </c>
@@ -1157,7 +1162,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="7" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1176,7 +1181,7 @@
       <c r="H13" s="6" t="n">
         <v>210.5</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="8">
         <f>(H13-G13)/G13</f>
         <v/>
       </c>
@@ -1212,7 +1217,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="7" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1231,7 +1236,7 @@
       <c r="H14" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="8">
         <f>(H14-G14)/G14</f>
         <v/>
       </c>
@@ -1268,7 +1273,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="7" t="n">
         <v>46269.41666666666</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1287,7 +1292,7 @@
       <c r="H15" s="2" t="n">
         <v>1445</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="8">
         <f>(H15-G15)/G15</f>
         <v/>
       </c>
@@ -1324,7 +1329,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="7" t="n">
         <v>46269.58333333334</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1343,7 +1348,7 @@
       <c r="H16" s="6" t="n">
         <v>208.5</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="8">
         <f>(H16-G16)/G16</f>
         <v/>
       </c>
@@ -1379,7 +1384,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="7" t="n">
         <v>46272.41666666666</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1398,7 +1403,7 @@
       <c r="H17" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="8">
         <f>(H17-G17)/G17</f>
         <v/>
       </c>
@@ -1435,7 +1440,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="7" t="n">
         <v>46272.41666666666</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1454,7 +1459,7 @@
       <c r="H18" s="2" t="n">
         <v>1455</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="8">
         <f>(H18-G18)/G18</f>
         <v/>
       </c>
@@ -1491,7 +1496,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="7" t="n">
         <v>46272.5</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1510,7 +1515,7 @@
       <c r="H19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="8">
         <f>(H19-G19)/G19</f>
         <v/>
       </c>
@@ -1547,7 +1552,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="7" t="n">
         <v>46273.41666666666</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1566,7 +1571,7 @@
       <c r="H20" s="6" t="n">
         <v>193.5</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="8">
         <f>(H20-G20)/G20</f>
         <v/>
       </c>
@@ -1603,7 +1608,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="7" t="n">
         <v>46274.41666666666</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1622,7 +1627,7 @@
       <c r="H21" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="8">
         <f>(H21-G21)/G21</f>
         <v/>
       </c>
@@ -1659,7 +1664,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="7" t="n">
         <v>46274.41666666666</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1678,7 +1683,7 @@
       <c r="H22" s="2" t="n">
         <v>1435</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="8">
         <f>(H22-G22)/G22</f>
         <v/>
       </c>
@@ -1715,7 +1720,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="7" t="n">
         <v>46274.66666666666</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1734,7 +1739,7 @@
       <c r="H23" s="6" t="n">
         <v>187.5</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="8">
         <f>(H23-G23)/G23</f>
         <v/>
       </c>
@@ -1771,7 +1776,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="7" t="n">
         <v>46275.45833333334</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1790,7 +1795,7 @@
       <c r="H24" s="6" t="n">
         <v>120.5</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="8">
         <f>(H24-G24)/G24</f>
         <v/>
       </c>
@@ -1826,7 +1831,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="7" t="n">
         <v>46276.41666666666</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1845,7 +1850,7 @@
       <c r="H25" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="8">
         <f>(H25-G25)/G25</f>
         <v/>
       </c>
@@ -1881,7 +1886,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="7" t="n">
         <v>46276.41666666666</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1900,7 +1905,7 @@
       <c r="H26" s="2" t="n">
         <v>1445</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="8">
         <f>(H26-G26)/G26</f>
         <v/>
       </c>
@@ -1936,7 +1941,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="7" t="n">
         <v>46276.45833333334</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1955,7 +1960,7 @@
       <c r="H27" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="8">
         <f>(H27-G27)/G27</f>
         <v/>
       </c>
@@ -1991,7 +1996,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="7" t="n">
         <v>46276.58333333334</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2010,7 +2015,7 @@
       <c r="H28" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="8">
         <f>(H28-G28)/G28</f>
         <v/>
       </c>
@@ -2046,7 +2051,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="7" t="n">
         <v>46276.625</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2065,7 +2070,7 @@
       <c r="H29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="8">
         <f>(H29-G29)/G29</f>
         <v/>
       </c>
@@ -2101,7 +2106,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="7" t="n">
         <v>46279.41666666666</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2120,7 +2125,7 @@
       <c r="H30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="8">
         <f>(H30-G30)/G30</f>
         <v/>
       </c>
@@ -2156,7 +2161,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="7" t="n">
         <v>46279.41666666666</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2175,7 +2180,7 @@
       <c r="H31" s="2" t="n">
         <v>1420</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="8">
         <f>(H31-G31)/G31</f>
         <v/>
       </c>
@@ -2211,7 +2216,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="7" t="n">
         <v>46279.45833333334</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2230,7 +2235,7 @@
       <c r="H32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="8">
         <f>(H32-G32)/G32</f>
         <v/>
       </c>
@@ -2266,7 +2271,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="7" t="n">
         <v>46279.58333333334</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2285,7 +2290,7 @@
       <c r="H33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="8">
         <f>(H33-G33)/G33</f>
         <v/>
       </c>
@@ -2321,7 +2326,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="7" t="n">
         <v>46279.625</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2340,7 +2345,7 @@
       <c r="H34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="8">
         <f>(H34-G34)/G34</f>
         <v/>
       </c>
@@ -2376,7 +2381,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="7" t="n">
         <v>46280.41666666666</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2395,7 +2400,7 @@
       <c r="H35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="8">
         <f>(H35-G35)/G35</f>
         <v/>
       </c>
@@ -2431,7 +2436,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="7" t="n">
         <v>46280.58333333334</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2450,7 +2455,7 @@
       <c r="H36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="8">
         <f>(H36-G36)/G36</f>
         <v/>
       </c>
@@ -2486,7 +2491,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="7" t="n">
         <v>46281.41666666666</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2505,7 +2510,7 @@
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="8">
         <f>(H37-G37)/G37</f>
         <v/>
       </c>
@@ -2541,7 +2546,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="7" t="n">
         <v>46281.41666666666</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2560,7 +2565,7 @@
       <c r="H38" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="8">
         <f>(H38-G38)/G38</f>
         <v/>
       </c>
@@ -2596,7 +2601,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="7" t="n">
         <v>46281.58333333334</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2615,7 +2620,7 @@
       <c r="H39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="8">
         <f>(H39-G39)/G39</f>
         <v/>
       </c>
@@ -2651,7 +2656,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="7" t="n">
         <v>46282.41666666666</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2670,7 +2675,7 @@
       <c r="H40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="8">
         <f>(H40-G40)/G40</f>
         <v/>
       </c>
@@ -2706,7 +2711,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="7" t="n">
         <v>46282.58333333334</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2725,7 +2730,7 @@
       <c r="H41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="8">
         <f>(H41-G41)/G41</f>
         <v/>
       </c>
@@ -2761,7 +2766,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="7" t="n">
         <v>46283.41666666666</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2780,7 +2785,7 @@
       <c r="H42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="8">
         <f>(H42-G42)/G42</f>
         <v/>
       </c>
@@ -2816,7 +2821,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="7" t="n">
         <v>46283.41666666666</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2835,7 +2840,7 @@
       <c r="H43" s="2" t="n">
         <v>1255</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="8">
         <f>(H43-G43)/G43</f>
         <v/>
       </c>
@@ -2871,7 +2876,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="7" t="n">
         <v>46283.58333333334</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2890,7 +2895,7 @@
       <c r="H44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="8">
         <f>(H44-G44)/G44</f>
         <v/>
       </c>
@@ -2926,7 +2931,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="7" t="n">
         <v>46286.41666666666</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2945,7 +2950,7 @@
       <c r="H45" s="2" t="n">
         <v>1295</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="8">
         <f>(H45-G45)/G45</f>
         <v/>
       </c>
@@ -2981,7 +2986,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="7" t="n">
         <v>46286.41666666666</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -3000,7 +3005,7 @@
       <c r="H46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="8">
         <f>(H46-G46)/G46</f>
         <v/>
       </c>
@@ -3036,7 +3041,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="7" t="n">
         <v>46286.58333333334</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -3055,7 +3060,7 @@
       <c r="H47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="8">
         <f>(H47-G47)/G47</f>
         <v/>
       </c>
@@ -3091,7 +3096,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="7" t="n">
         <v>46287.41666666666</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -3110,7 +3115,7 @@
       <c r="H48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="8">
         <f>(H48-G48)/G48</f>
         <v/>
       </c>
@@ -3146,7 +3151,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="7" t="n">
         <v>46287.58333333334</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -3165,7 +3170,7 @@
       <c r="H49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I49" s="8">
         <f>(H49-G49)/G49</f>
         <v/>
       </c>
@@ -3201,7 +3206,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="7" t="n">
         <v>46288.41666666666</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -3220,7 +3225,7 @@
       <c r="H50" s="2" t="n">
         <v>1290</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I50" s="8">
         <f>(H50-G50)/G50</f>
         <v/>
       </c>
@@ -3256,7 +3261,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="7" t="n">
         <v>46288.41666666666</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -3275,7 +3280,7 @@
       <c r="H51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I51" s="8">
         <f>(H51-G51)/G51</f>
         <v/>
       </c>
@@ -3311,7 +3316,7 @@
           <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
         </is>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="7" t="n">
         <v>46288.58333333334</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -3330,7 +3335,7 @@
       <c r="H52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I52" s="8">
         <f>(H52-G52)/G52</f>
         <v/>
       </c>
@@ -3366,7 +3371,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="7" t="n">
         <v>46290.41666666666</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -3385,7 +3390,7 @@
       <c r="H53" s="2" t="n">
         <v>1285</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I53" s="8">
         <f>(H53-G53)/G53</f>
         <v/>
       </c>
@@ -3421,7 +3426,7 @@
           <t>额尔登特矿业公司国资企业</t>
         </is>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="7" t="n">
         <v>46290.625</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -3440,7 +3445,7 @@
       <c r="H54" s="6" t="n">
         <v>3613.59</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I54" s="8">
         <f>(H54-G54)/G54</f>
         <v/>
       </c>
@@ -3476,7 +3481,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="7" t="n">
         <v>46293.41666666666</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -3495,7 +3500,7 @@
       <c r="H55" s="2" t="n">
         <v>1260</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I55" s="8">
         <f>(H55-G55)/G55</f>
         <v/>
       </c>
@@ -3531,7 +3536,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="7" t="n">
         <v>46295.41666666666</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -3550,7 +3555,7 @@
       <c r="H56" s="2" t="n">
         <v>1265</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I56" s="8">
         <f>(H56-G56)/G56</f>
         <v/>
       </c>
@@ -3586,7 +3591,7 @@
           <t>坎加德勘探 有限责任公司</t>
         </is>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="7" t="n">
         <v>46296.58333333334</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3605,7 +3610,7 @@
       <c r="H57" s="2" t="n">
         <v>540</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I57" s="8">
         <f>(H57-G57)/G57</f>
         <v/>
       </c>
@@ -3641,7 +3646,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="7" t="n">
         <v>46297.41666666666</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -3660,7 +3665,7 @@
       <c r="H58" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="I58" s="5">
+      <c r="I58" s="8">
         <f>(H58-G58)/G58</f>
         <v/>
       </c>
@@ -3696,7 +3701,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="7" t="n">
         <v>46297.41666666666</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -3715,7 +3720,7 @@
       <c r="H59" s="2" t="n">
         <v>1265</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="8">
         <f>(H59-G59)/G59</f>
         <v/>
       </c>
@@ -3751,7 +3756,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="7" t="n">
         <v>46300.41666666666</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3770,7 +3775,7 @@
       <c r="H60" s="2" t="n">
         <v>1255</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I60" s="8">
         <f>(H60-G60)/G60</f>
         <v/>
       </c>
@@ -3806,7 +3811,7 @@
           <t>塔万陶勒盖股份公司</t>
         </is>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="7" t="n">
         <v>46301.41666666666</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -3825,7 +3830,7 @@
       <c r="H61" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="I61" s="5">
+      <c r="I61" s="8">
         <f>(H61-G61)/G61</f>
         <v/>
       </c>
@@ -3861,7 +3866,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="7" t="n">
         <v>46302.41666666666</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -3880,7 +3885,7 @@
       <c r="H62" s="2" t="n">
         <v>1250</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I62" s="8">
         <f>(H62-G62)/G62</f>
         <v/>
       </c>
@@ -3916,7 +3921,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="7" t="n">
         <v>46304.41666666666</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -3935,7 +3940,7 @@
       <c r="H63" s="2" t="n">
         <v>1260</v>
       </c>
-      <c r="I63" s="5">
+      <c r="I63" s="8">
         <f>(H63-G63)/G63</f>
         <v/>
       </c>
@@ -3971,7 +3976,7 @@
           <t>能源资源有限责任公司</t>
         </is>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="7" t="n">
         <v>46307.41666666666</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -3990,7 +3995,7 @@
       <c r="H64" s="2" t="n">
         <v>1260</v>
       </c>
-      <c r="I64" s="5">
+      <c r="I64" s="8">
         <f>(H64-G64)/G64</f>
         <v/>
       </c>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -456,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4015,6 +4016,59 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>46309.41666666666</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="8">
+        <f>(H65-G65)/G65</f>
+        <v/>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月11日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4048,7 +4048,9 @@
       <c r="G65" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H65" s="2" t="n"/>
+      <c r="H65" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I65" s="8">
         <f>(H65-G65)/G65</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4049,7 +4049,7 @@
         <v>1150</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>1150</v>
+        <v>1250</v>
       </c>
       <c r="I65" s="8">
         <f>(H65-G65)/G65</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -456,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4070,6 +4071,59 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>46311.41666666666</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="8">
+        <f>(H66-G66)/G66</f>
+        <v/>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月13日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4103,7 +4103,9 @@
       <c r="G66" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H66" s="2" t="n"/>
+      <c r="H66" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I66" s="8">
         <f>(H66-G66)/G66</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4104,7 +4104,7 @@
         <v>1150</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>1150</v>
+        <v>1260</v>
       </c>
       <c r="I66" s="8">
         <f>(H66-G66)/G66</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -456,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4125,6 +4126,59 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>46314.41666666666</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="8">
+        <f>(H67-G67)/G67</f>
+        <v/>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月16日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4158,7 +4158,9 @@
       <c r="G67" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H67" s="2" t="n"/>
+      <c r="H67" s="2" t="n">
+        <v>1155</v>
+      </c>
       <c r="I67" s="8">
         <f>(H67-G67)/G67</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4159,7 +4159,7 @@
         <v>1150</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1155</v>
+        <v>1235</v>
       </c>
       <c r="I67" s="8">
         <f>(H67-G67)/G67</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -456,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4180,6 +4181,112 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>46316.41666666666</v>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="8">
+        <f>(H68-G68)/G68</f>
+        <v/>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月18日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>中挥发份性焦煤</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>46316.45833333334</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>5 批量/32000吨/</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>177.7</v>
+      </c>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="8">
+        <f>(H69-G69)/G69</f>
+        <v/>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>4/21/2027 /根据供应计划,在送货时间内完成供应/</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>供应商送到买方指定的中国甘其毛都口岸的海关监管区</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>公路， 铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4213,7 +4213,9 @@
       <c r="G68" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H68" s="2" t="n"/>
+      <c r="H68" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I68" s="8">
         <f>(H68-G68)/G68</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4214,7 +4214,7 @@
         <v>1150</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>1150</v>
+        <v>1240</v>
       </c>
       <c r="I68" s="8">
         <f>(H68-G68)/G68</f>
@@ -4268,7 +4268,9 @@
       <c r="G69" s="2" t="n">
         <v>177.7</v>
       </c>
-      <c r="H69" s="2" t="n"/>
+      <c r="H69" s="2" t="n">
+        <v>177.7</v>
+      </c>
       <c r="I69" s="8">
         <f>(H69-G69)/G69</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4291,6 +4291,59 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>洗选半软焦煤</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>46317.45833333334</v>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>5 批量/32000吨/</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="8">
+        <f>(H70-G70)/G70</f>
+        <v/>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>1/22/2027 /根据供应计划,在送货时间内完成供应/</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>供应商送到买方指定的中国满都拉口岸的海关监管区</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>公路， 铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4323,7 +4323,9 @@
       <c r="G70" s="2" t="n">
         <v>182.9</v>
       </c>
-      <c r="H70" s="2" t="n"/>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="I70" s="8">
         <f>(H70-G70)/G70</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4346,6 +4346,112 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>46318.41666666666</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="8">
+        <f>(H71-G71)/G71</f>
+        <v/>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月20日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1/3焦煤</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>46318.45833333334</v>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>5 批量/32000吨/</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="8">
+        <f>(H72-G72)/G72</f>
+        <v/>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>1/23/2027 /根据供应计划,在送货时间内完成供应/</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>供应商送到买方指定的中国满都拉口岸的海关监管区</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>公路， 铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4378,7 +4378,9 @@
       <c r="G71" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H71" s="2" t="n"/>
+      <c r="H71" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I71" s="8">
         <f>(H71-G71)/G71</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4379,7 +4379,7 @@
         <v>1150</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>1150</v>
+        <v>1245</v>
       </c>
       <c r="I71" s="8">
         <f>(H71-G71)/G71</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4433,7 +4433,9 @@
       <c r="G72" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="H72" s="2" t="n"/>
+      <c r="H72" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="I72" s="8">
         <f>(H72-G72)/G72</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -456,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4455,6 +4456,112 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>46321.41666666666</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="8">
+        <f>(H73-G73)/G73</f>
+        <v/>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月23日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>中挥发份性焦煤</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>46321.45833333334</v>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>5 批量/32000吨/</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="H74" s="2" t="n"/>
+      <c r="I74" s="8">
+        <f>(H74-G74)/G74</f>
+        <v/>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>1/26/2027 /根据供应计划,在送货时间内完成供应/</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>供应商送到买方指定的中国满都拉口岸的海关监管区</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>公路， 铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4488,7 +4488,9 @@
       <c r="G73" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H73" s="2" t="n"/>
+      <c r="H73" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I73" s="8">
         <f>(H73-G73)/G73</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4489,7 +4489,7 @@
         <v>1150</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>1150</v>
+        <v>1205</v>
       </c>
       <c r="I73" s="8">
         <f>(H73-G73)/G73</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4543,7 +4543,9 @@
       <c r="G74" s="2" t="n">
         <v>181.8</v>
       </c>
-      <c r="H74" s="2" t="n"/>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="I74" s="8">
         <f>(H74-G74)/G74</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4566,6 +4566,59 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>洗选半软焦煤</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>46322.45833333334</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>5 批量/32000吨/</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="8">
+        <f>(H75-G75)/G75</f>
+        <v/>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>4/27/2027 /根据供应计划,在送货时间内完成供应/</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>供应商送到买方指定的中国甘其毛都口岸的海关监管区</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>公路， 铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4598,7 +4598,9 @@
       <c r="G75" s="2" t="n">
         <v>167.6</v>
       </c>
-      <c r="H75" s="2" t="n"/>
+      <c r="H75" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="I75" s="8">
         <f>(H75-G75)/G75</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4621,6 +4621,112 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>46323.41666666666</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="8">
+        <f>(H76-G76)/G76</f>
+        <v/>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月25日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>铜</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>铜含量为22.35%的铜精矿</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>额尔登特矿业公司国资企业</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>46323.625</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>7 批量/6342吨/</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>3341.49</v>
+      </c>
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="8">
+        <f>(H77-G77)/G77</f>
+        <v/>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>將於2026年12月31日前交付。 DAP (国际贸易术语解释通则2020及其任何修订) 蒙古/中国边境 (二连)。</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>中国二连站铜矿粉装卸区</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4653,7 +4653,9 @@
       <c r="G76" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H76" s="2" t="n"/>
+      <c r="H76" s="2" t="n">
+        <v>1155</v>
+      </c>
       <c r="I76" s="8">
         <f>(H76-G76)/G76</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4654,7 +4654,7 @@
         <v>1150</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>1155</v>
+        <v>1225</v>
       </c>
       <c r="I76" s="8">
         <f>(H76-G76)/G76</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4708,7 +4708,9 @@
       <c r="G77" s="2" t="n">
         <v>3341.49</v>
       </c>
-      <c r="H77" s="2" t="n"/>
+      <c r="H77" s="2" t="n">
+        <v>3341.49</v>
+      </c>
       <c r="I77" s="8">
         <f>(H77-G77)/G77</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4709,7 +4709,7 @@
         <v>3341.49</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>3341.49</v>
+        <v>3351.49</v>
       </c>
       <c r="I77" s="8">
         <f>(H77-G77)/G77</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4731,6 +4731,59 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>1/3焦煤</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>46324.45833333334</v>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>5 批量/32000吨/</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="8">
+        <f>(H78-G78)/G78</f>
+        <v/>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>4/29/2027 /根据供应计划,在送货时间内完成供应/</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>供应商送到买方指定的中国甘其毛都口岸的海关监管区</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>公路， 铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4763,7 +4763,9 @@
       <c r="G78" s="2" t="n">
         <v>163.9</v>
       </c>
-      <c r="H78" s="2" t="n"/>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="I78" s="8">
         <f>(H78-G78)/G78</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4786,6 +4786,112 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>洗精主焦煤</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>能源资源有限责任公司</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>46325.41666666666</v>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>2 批量/12800吨/</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="8">
+        <f>(H79-G79)/G79</f>
+        <v/>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>2027年2月27日（最后供货日） DAP甘其毛都口岸</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>买方指定的甘其毛都口岸海关监管区</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>公路运输</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1/3焦煤</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>埃尔登内斯·塔万陶勒盖有限责任公司</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>46325.45833333334</v>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>5 批量/32000吨/</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="8">
+        <f>(H80-G80)/G80</f>
+        <v/>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>4/30/2027 /根据供应计划,在送货时间内完成供应/</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>供应商送到买方指定的中国甘其毛都口岸的海关监管区</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>公路， 铁路</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4818,7 +4818,9 @@
       <c r="G79" s="2" t="n">
         <v>1150</v>
       </c>
-      <c r="H79" s="2" t="n"/>
+      <c r="H79" s="2" t="n">
+        <v>1150</v>
+      </c>
       <c r="I79" s="8">
         <f>(H79-G79)/G79</f>
         <v/>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4819,7 +4819,7 @@
         <v>1150</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>1150</v>
+        <v>1210</v>
       </c>
       <c r="I79" s="8">
         <f>(H79-G79)/G79</f>

--- a/data/蒙煤拍卖临时记录.xlsx
+++ b/data/蒙煤拍卖临时记录.xlsx
@@ -4873,7 +4873,9 @@
       <c r="G80" s="2" t="n">
         <v>107.3</v>
       </c>
-      <c r="H80" s="2" t="n"/>
+      <c r="H80" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="I80" s="8">
         <f>(H80-G80)/G80</f>
         <v/>
